--- a/main/ig/StructureDefinition-tlsv-observation.xlsx
+++ b/main/ig/StructureDefinition-tlsv-observation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-03T11:18:09+00:00</t>
+    <t>2026-06-26T11:58:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
